--- a/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:11</t>
+          <t>2026-10-14 00:26:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:12</t>
+          <t>2026-10-14 00:26:59</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:10:14</t>
+          <t>2026-10-14 00:27:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:57</t>
+          <t>2026-10-14 01:01:18</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 00:26:59</t>
+          <t>2026-10-14 01:01:19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 00:27:00</t>
+          <t>2026-10-14 01:01:21</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-3.1%5940</t>
+          <t>-0.93%5885</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>5940</v>
+        <v>5885</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.00%323,000</t>
+          <t>7.91%323,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.00%</t>
+          <t>7.91%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%1440</t>
+          <t>-0.69%1430</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.69%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1440</v>
+        <v>1430</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.80%1,299,000</t>
+          <t>7.73%1,299,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.80%</t>
+          <t>7.73%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.37%6990</t>
+          <t>+1.14%7070</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.37%</t>
+          <t>+1.14%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>6990</v>
+        <v>7070</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7.57%260,000</t>
+          <t>7.65%260,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7.57%</t>
+          <t>7.65%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.18%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-5.98%1180</t>
+          <t>+0.42%1185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-5.98%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>1180</v>
+        <v>1185</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7.52%1,530,000</t>
+          <t>7.54%1,530,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>7.52%</t>
+          <t>7.54%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.03%2260</t>
+          <t>-1.11%2235</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-4.03%</t>
+          <t>-1.11%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>2260</v>
+        <v>2235</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>6.26%665,000</t>
+          <t>6.18%665,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6.26%</t>
+          <t>6.18%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.06%8095</t>
+          <t>+1.85%8245</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+1.85%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8095</v>
+        <v>8245</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.84%173,000</t>
+          <t>5.93%173,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.84%</t>
+          <t>5.93%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.95%17350</t>
+          <t>+7.69%1260</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+7.69%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>17350</v>
+        <v>1260</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5.73%79,300</t>
+          <t>5.91%1,127,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.73%</t>
+          <t>5.91%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>79300</v>
+        <v>1127000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-2.16%4525</t>
+          <t>+0.86%17500</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-2.16%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>4525</v>
+        <v>17500</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5.54%294,000</t>
+          <t>5.77%79,300</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.54%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>294000</v>
+        <v>79300</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.26%1170</t>
+          <t>-1.1%4475</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.26%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1170</v>
+        <v>4475</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5.50%1,127,000</t>
+          <t>5.47%294,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.50%</t>
+          <t>5.47%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1127000</v>
+        <v>294000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.23%2040</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-4.23%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5.18%609,000</t>
+          <t>5.19%609,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.18%</t>
+          <t>5.19%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.22%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-9.84%5545</t>
+          <t>-0.45%5520</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.84%</t>
+          <t>-0.45%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>5545</v>
+        <v>5520</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.90%212,000</t>
+          <t>4.87%212,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4.90%</t>
+          <t>4.87%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.52%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,25 +1180,25 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.22%926</t>
+          <t>-0.32%923</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>926</v>
+        <v>923</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.98%1,030,000</t>
+          <t>3.95%1,030,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.98%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-3.1%3280</t>
+          <t>+1.07%3315</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>+1.07%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>3280</v>
+        <v>3315</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.80%278,000</t>
+          <t>3.83%278,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-2.64%2210</t>
+          <t>-0.68%2195</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-2.64%</t>
+          <t>-0.68%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2210</v>
+        <v>2195</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3.14%341,000</t>
+          <t>3.11%341,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.11%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:18</t>
+          <t>2026-10-14 21:56:28</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.47%6070</t>
+          <t>-4.78%5780</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-6.47%</t>
+          <t>-4.78%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>6070</v>
+        <v>5780</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.04%120,000</t>
+          <t>2.88%120,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>2.88%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.61%1655</t>
+          <t>+4.83%1735</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-4.61%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1655</v>
+        <v>1735</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2.11%306,000</t>
+          <t>2.21%306,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2.11%</t>
+          <t>2.21%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.91%10060</t>
+          <t>-0.55%10005</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-0.55%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10060</v>
+        <v>10005</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.10%50,000</t>
+          <t>2.08%50,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-1.97%2490</t>
+          <t>0%2490</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-1.97%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.86%179,000</t>
+          <t>1.85%179,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,25 +1607,25 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-0.29%1715</t>
+          <t>-1.75%1685</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-0.29%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1715</v>
+        <v>1685</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.43%200,000</t>
+          <t>1.40%200,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,25 +1668,25 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.48%1600</t>
+          <t>-3.75%1540</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-4.48%</t>
+          <t>-3.75%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1600</v>
+        <v>1540</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.99%148,000</t>
+          <t>0.95%148,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,25 +1729,25 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-3.52%2195</t>
+          <t>-3.64%2115</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-3.52%</t>
+          <t>-3.64%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2195</v>
+        <v>2115</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.91%99,139</t>
+          <t>0.87%99,139</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.58%1775</t>
+          <t>+0.56%1785</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-6.58%</t>
+          <t>+0.56%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1775</v>
+        <v>1785</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,25 +1851,25 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-5.39%5700</t>
+          <t>-1.49%5615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-5.39%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5700</v>
+        <v>5615</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.55%23,000</t>
+          <t>0.54%23,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.55%</t>
+          <t>0.54%</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,25 +1912,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%783</t>
+          <t>+2.43%802</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.43%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>783</v>
+        <v>802</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.48%146,000</t>
+          <t>0.49%146,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-1.89%1040</t>
+          <t>+0.96%1050</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.31%175</t>
+          <t>+0.57%176</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,25 +2095,25 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.45%246.5</t>
+          <t>+2.64%253</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-6.45%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>246.5</v>
+        <v>253</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.10%100,000</t>
+          <t>0.11%100,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.11%</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+1.67%305</t>
+          <t>-2.79%296.5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+1.67%</t>
+          <t>-2.79%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>305</v>
+        <v>296.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.47%268.5</t>
+          <t>+3.54%278</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.47%</t>
+          <t>+3.54%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>268.5</v>
+        <v>278</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:19</t>
+          <t>2026-10-14 21:56:29</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-0.68%7275</t>
+          <t>-5.43%6880</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-0.68%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>7275</v>
+        <v>6880</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.63%544</t>
+          <t>-1.29%537</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.63%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,25 +2395,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-7.74%4055</t>
+          <t>+0.35%142</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-7.74%</t>
+          <t>+0.35%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>4055</v>
+        <v>142</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.02%1,000</t>
+          <t>0.02%28,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2422,11 +2422,11 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,25 +2456,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-2.75%141.5</t>
+          <t>-2.84%3940</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-2.75%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>141.5</v>
+        <v>3940</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.02%28,000</t>
+          <t>0.02%1,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2483,7 +2483,7 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>28000</v>
+        <v>1000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-0.42%718</t>
+          <t>-0.56%714</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-0.42%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.24%3275</t>
+          <t>-1.53%3225</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>3275</v>
+        <v>3225</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.12%264</t>
+          <t>+9.85%290</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.12%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>264</v>
+        <v>290</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-8.86%473</t>
+          <t>+5.71%500</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.86%</t>
+          <t>+5.71%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>&lt;0.01%5,000</t>
+          <t>0.01%5,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.69%1165</t>
+          <t>+2.15%1190</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.69%</t>
+          <t>+2.15%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>1165</v>
+        <v>1190</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-2.89%740</t>
+          <t>+0.95%747</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-2.89%</t>
+          <t>+0.95%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-1.06%1860</t>
+          <t>+4.03%1935</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>+4.03%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1860</v>
+        <v>1935</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+2.23%183</t>
+          <t>+2.19%187</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+2.19%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+5.28%319</t>
+          <t>+9.4%349</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+5.28%</t>
+          <t>+9.4%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-4.92%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-4.92%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-3.31%1170</t>
+          <t>+1.28%1185</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-3.31%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1170</v>
+        <v>1185</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 01:01:21</t>
+          <t>2026-10-14 21:56:31</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-5.69%116</t>
+          <t>+0.86%117</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.69%</t>
+          <t>+0.86%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:28</t>
+          <t>2026-10-14 22:02:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:29</t>
+          <t>2026-10-14 22:02:07</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 21:56:31</t>
+          <t>2026-10-14 22:02:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">

--- a/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-14_00405A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:06</t>
+          <t>2026-10-14 22:32:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:07</t>
+          <t>2026-10-14 22:32:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-14 22:02:09</t>
+          <t>2026-10-14 22:32:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
